--- a/docs/SFR_반영점검표.xlsx
+++ b/docs/SFR_반영점검표.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>components/solar-edu/JourneyPanel.tsx, EDU_FACTS 롤링</t>
+          <t>JourneyPanel.tsx · mocks/eduContent.ts 수준별 주제·티커 문구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>components/solar-edu/ImpactPanel.tsx, utils/eco.ts</t>
+          <t>ImpactPanel.tsx, utils/eco.ts · 수준별 환산 항목 3~4종</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>HeadlineStrip.tsx, EDU_FACTS</t>
+          <t>초·중·고 3수준(mocks/eduContent.ts). 학교급 자동 매핑 + ?level= 고정 + 화면 세그먼트로 전환</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>GrowingTree.tsx, SunPathArt.tsx</t>
+          <t>GrowingTree.tsx, SunPathArt.tsx, 초등판 DayStoryPanel.tsx 해 크기 변화</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Reports/components/MonthlyTab.tsx 발전소 정보</t>
+          <t>보고서 1장(monthly/ReportSheet.tsx) 발전소 정보 표</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>같은 화면</t>
+          <t>2장 TrendChart — 금월·전월 일별 발전량 곡선</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>같은 화면</t>
+          <t>2장 InverterHoursChart — 인버터별 일별 발전시간</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>seriesPalette</t>
+          <t>seriesPalette 색 + SERIES_DASH 선 모양</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>usePrint (브라우저 인쇄 → PDF)</t>
+          <t>useReportPdf — A4 지면을 장마다 캡처해 PDF 한 장씩 담음. 브라우저 인쇄도 유지</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>MonthlyTab.tsx 인버터별 AI 진단 결과</t>
+          <t>인버터마다 한 장, DiagnosisChart — 일별 정상범위 띠 위에 측정값</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>같은 화면 스트링·접속반 단위 진단</t>
+          <t>같은 장 StringEfficiencyChart — 회로별 일별 효율(정상범위 88~104%)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>같은 화면</t>
+          <t>같은 장 고장분류 표(발생일 묶음)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>usePrint</t>
+          <t>useReportPdf</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
